--- a/Result/profitability/4905.xlsx
+++ b/Result/profitability/4905.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.24</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5375</v>
+        <v>1.5</v>
       </c>
       <c r="N2" t="n">
-        <v>26.85625</v>
+        <v>26.73625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7212500000000001</v>
+        <v>1.3975</v>
       </c>
       <c r="N3" t="n">
-        <v>27.33125</v>
+        <v>28.5075</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.39</v>
       </c>
       <c r="M4" t="n">
-        <v>0.655</v>
+        <v>1.40125</v>
       </c>
       <c r="N4" t="n">
-        <v>29.45</v>
+        <v>28.64875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.24</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6400000000000001</v>
+        <v>1.66875</v>
       </c>
       <c r="N5" t="n">
-        <v>30.72375</v>
+        <v>31.4325</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>-0.14</v>
       </c>
       <c r="M6" t="n">
-        <v>0.86</v>
+        <v>1.23625</v>
       </c>
       <c r="N6" t="n">
-        <v>29.0275</v>
+        <v>29.33375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.09</v>
       </c>
       <c r="M7" t="n">
-        <v>0.43375</v>
+        <v>1.1025</v>
       </c>
       <c r="N7" t="n">
-        <v>30.025</v>
+        <v>30.19875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.16</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2912500000000001</v>
+        <v>0.86375</v>
       </c>
       <c r="N8" t="n">
-        <v>31.22</v>
+        <v>31.11125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>-0.03</v>
       </c>
       <c r="M9" t="n">
-        <v>0.06875000000000005</v>
+        <v>0.06874999999999999</v>
       </c>
       <c r="N9" t="n">
         <v>32.92749999999999</v>
@@ -1645,7 +1645,7 @@
         <v>0.12</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05375000000000005</v>
+        <v>0.05374999999999999</v>
       </c>
       <c r="N10" t="n">
         <v>32.75125</v>
@@ -1772,7 +1772,7 @@
         <v>0.77</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1375000000000001</v>
+        <v>0.1375</v>
       </c>
       <c r="N11" t="n">
         <v>33.24125</v>
@@ -2026,7 +2026,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2475000000000001</v>
+        <v>0.2475</v>
       </c>
       <c r="N13" t="n">
         <v>34.57375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4905</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>237</v>
+      </c>
+      <c r="D75" t="n">
+        <v>173</v>
+      </c>
+      <c r="E75" t="n">
+        <v>64</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-2.45%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>207</v>
+      </c>
+      <c r="J75" t="n">
+        <v>202</v>
+      </c>
+      <c r="K75" t="n">
+        <v>185</v>
+      </c>
+      <c r="L75" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.29875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>25.545</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.617142857142857</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.870000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03135135135135136</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-4.331578947368421</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.669999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2673267326732671</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
